--- a/education_forms/038_educator_climate_change_literacy_registration_form--education_forms.xlsx
+++ b/education_forms/038_educator_climate_change_literacy_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Full Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>institution</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Institution</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>institution</t>
+          <t>position</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Institution</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,64 +635,64 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>position</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>State</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>country</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,41 +704,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>agree_terms</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>I agree to the Terms and Conditions</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>agree_terms</t>
+          <t>agree_privacy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>I agree to the Terms and Conditions</t>
+          <t>I agree to the Privacy Policy</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,320 +768,44 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>agree_privacy</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>I agree to the Privacy Policy</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>institution</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Institution</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>position</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'alabama'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Alabama'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -1148,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'alaska'}</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Alaska'}</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
@@ -1165,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'american_samoa'}</t>
+          <t>american_samoa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'American Samoa'}</t>
+          <t>American Samoa</t>
         </is>
       </c>
     </row>
@@ -1182,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'arizona'}</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Arizona'}</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -1199,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'arkansas'}</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Arkansas'}</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -1216,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1233,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'colorado'}</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Colorado'}</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -1250,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'connecticut'}</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Connecticut'}</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -1267,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'delaware'}</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Delaware'}</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'district_of_columbia'}</t>
+          <t>district_of_columbia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'District of Columbia'}</t>
+          <t>District of Columbia</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'georgia'}</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Georgia'}</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'guam'}</t>
+          <t>guam</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Guam'}</t>
+          <t>Guam</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'hawaii'}</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Hawaii'}</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'idaho'}</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Idaho'}</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'illinois'}</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Illinois'}</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'indiana'}</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Indiana'}</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'iowa'}</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Iowa'}</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'kansas'}</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Kansas'}</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'kentucky'}</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Kentucky'}</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'louisiana'}</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Louisiana'}</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'maine'}</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Maine'}</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'maryland'}</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Maryland'}</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'massachusetts'}</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Massachusetts'}</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'michigan'}</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Michigan'}</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'minnesota'}</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Minnesota'}</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'mississippi'}</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Mississippi'}</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'missouri'}</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Missouri'}</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1331,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'montana'}</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Montana'}</t>
+          <t>Montana</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1348,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'nebraska'}</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Nebraska'}</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1365,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'nevada'}</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Nevada'}</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1382,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'new_hampshire'}</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'New Hampshire'}</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1399,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'new_jersey'}</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'New Jersey'}</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1416,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'new_mexico'}</t>
+          <t>new_mexico</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'New Mexico'}</t>
+          <t>New Mexico</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1433,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1450,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'north_carolina'}</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'North Carolina'}</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1467,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'north_dakota'}</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'North Dakota'}</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1484,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'northern_mariana_islands'}</t>
+          <t>northern_mariana_islands</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Northern Mariana Islands'}</t>
+          <t>Northern Mariana Islands</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1501,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'ohio'}</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Ohio'}</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1518,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'oklahoma'}</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Oklahoma'}</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1535,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'oregon'}</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Oregon'}</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1552,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'pennsylvania'}</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Pennsylvania'}</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1569,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'puerto_rico'}</t>
+          <t>puerto_rico</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Puerto Rico'}</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1586,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'rhode_island'}</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Rhode Island'}</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1603,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'south_carolina'}</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'South Carolina'}</t>
+          <t>South Carolina</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1620,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'south_dakota'}</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'South Dakota'}</t>
+          <t>South Dakota</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'tennessee'}</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Tennessee'}</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1654,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1671,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'utah'}</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Utah'}</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1688,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'vermont'}</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Vermont'}</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1705,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'virginia'}</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Virginia'}</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1722,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'washington'}</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Washington'}</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -2015,12 +1739,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'washington_d.c.'}</t>
+          <t>washington_d.c.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Washington D.C.'}</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
     </row>
@@ -2032,12 +1756,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'west_virginia'}</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'West Virginia'}</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -2049,12 +1773,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'wisconsin'}</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Wisconsin'}</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -2066,12 +1790,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'wyoming'}</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Wyoming'}</t>
+          <t>Wyoming</t>
         </is>
       </c>
     </row>
@@ -2083,12 +1807,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree_to_the_terms_and_conditions'}</t>
+          <t>i_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'I agree to the Terms and Conditions'}</t>
+          <t>I agree to the Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -2100,12 +1824,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_agree_to_the_terms_and_conditions'}</t>
+          <t>i_do_not_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'I do not agree to the Terms and Conditions'}</t>
+          <t>I do not agree to the Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -2117,12 +1841,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree_to_the_privacy_policy'}</t>
+          <t>i_agree_to_the_privacy_policy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'I agree to the Privacy Policy'}</t>
+          <t>I agree to the Privacy Policy</t>
         </is>
       </c>
     </row>
@@ -2134,964 +1858,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_agree_to_the_privacy_policy'}</t>
+          <t>i_do_not_agree_to_the_privacy_policy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'I do not agree to the Privacy Policy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>{'label':_'alabama'}</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>{'label': 'Alabama'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>{'label':_'alaska'}</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>{'label': 'Alaska'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>{'label':_'american_samoa'}</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>{'label': 'American Samoa'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>{'label':_'arizona'}</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>{'label': 'Arizona'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>{'label':_'arkansas'}</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>{'label': 'Arkansas'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>{'label':_'california'}</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>{'label': 'California'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>{'label':_'colorado'}</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>{'label': 'Colorado'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>{'label':_'connecticut'}</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>{'label': 'Connecticut'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>{'label':_'delaware'}</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>{'label': 'Delaware'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>{'label':_'district_of_columbia'}</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>{'label': 'District of Columbia'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>{'label':_'florida'}</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>{'label': 'Florida'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>{'label':_'georgia'}</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>{'label': 'Georgia'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>{'label':_'guam'}</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>{'label': 'Guam'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>{'label':_'hawaii'}</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>{'label': 'Hawaii'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>{'label':_'idaho'}</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>{'label': 'Idaho'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>{'label':_'illinois'}</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>{'label': 'Illinois'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>{'label':_'indiana'}</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>{'label': 'Indiana'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>{'label':_'iowa'}</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>{'label': 'Iowa'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>{'label':_'kansas'}</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>{'label': 'Kansas'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>{'label':_'kentucky'}</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>{'label': 'Kentucky'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>{'label':_'louisiana'}</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>{'label': 'Louisiana'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>{'label':_'maine'}</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>{'label': 'Maine'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>{'label':_'maryland'}</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>{'label': 'Maryland'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>{'label':_'massachusetts'}</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>{'label': 'Massachusetts'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>{'label':_'michigan'}</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>{'label': 'Michigan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>{'label':_'minnesota'}</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>{'label': 'Minnesota'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>{'label':_'mississippi'}</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>{'label': 'Mississippi'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>{'label':_'missouri'}</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>{'label': 'Missouri'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>{'label':_'montana'}</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>{'label': 'Montana'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>{'label':_'nebraska'}</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>{'label': 'Nebraska'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>{'label':_'nevada'}</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>{'label': 'Nevada'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>{'label':_'new_hampshire'}</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>{'label': 'New Hampshire'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>{'label':_'new_jersey'}</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>{'label': 'New Jersey'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>{'label':_'new_mexico'}</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>{'label': 'New Mexico'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>{'label':_'new_york'}</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>{'label': 'New York'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>{'label':_'north_carolina'}</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>{'label': 'North Carolina'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>{'label':_'north_dakota'}</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>{'label': 'North Dakota'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>{'label':_'northern_mariana_islands'}</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>{'label': 'Northern Mariana Islands'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>{'label':_'ohio'}</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>{'label': 'Ohio'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>{'label':_'oklahoma'}</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>{'label': 'Oklahoma'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>{'label':_'oregon'}</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>{'label': 'Oregon'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>{'label':_'pennsylvania'}</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>{'label': 'Pennsylvania'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>{'label':_'puerto_rico'}</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>{'label': 'Puerto Rico'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>{'label':_'rhode_island'}</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>{'label': 'Rhode Island'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>{'label':_'south_carolina'}</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>{'label': 'South Carolina'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>{'label':_'south_dakota'}</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>{'label': 'South Dakota'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>{'label':_'tennessee'}</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>{'label': 'Tennessee'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>{'label':_'texas'}</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>{'label': 'Texas'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>{'label':_'utah'}</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>{'label': 'Utah'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>{'label':_'vermont'}</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>{'label': 'Vermont'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>{'label':_'virginia'}</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>{'label': 'Virginia'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>{'label':_'washington'}</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>{'label': 'Washington'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>{'label':_'washington_d.c.'}</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>{'label': 'Washington D.C.'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>{'label':_'west_virginia'}</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>{'label': 'West Virginia'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>{'label':_'wisconsin'}</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>{'label': 'Wisconsin'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>{'label':_'wyoming'}</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>{'label': 'Wyoming'}</t>
+          <t>I do not agree to the Privacy Policy</t>
         </is>
       </c>
     </row>
